--- a/diseases/d163/2026-2029.xlsx
+++ b/diseases/d163/2026-2029.xlsx
@@ -29331,12 +29331,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -29361,22 +29361,22 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>0.1308283259959668</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -29423,42 +29423,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29490,12 +29490,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -29520,38 +29520,38 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Nephropathia epidemica</t>
+          <t>Sorkfeber</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -29611,17 +29611,17 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Swedish source category is nephropathia epidemica.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -29644,7 +29644,7 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="AT151" t="n">
@@ -29657,40 +29657,433 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW151" t="inlineStr">
+      <c r="AW152" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX151" t="inlineStr">
+      <c r="AX152" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY151" t="inlineStr">
+      <c r="AY152" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ151" t="inlineStr">
+      <c r="AZ152" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA151" t="inlineStr">
+      <c r="BA152" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB151" t="inlineStr">
+      <c r="BB152" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC151" t="inlineStr">
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Nephropathia epidemica</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -29812,7 +30205,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -29822,7 +30215,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -29842,7 +30235,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -29874,7 +30267,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>771</v>
+        <v>785</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d163/2026-2029.xlsx
+++ b/diseases/d163/2026-2029.xlsx
@@ -25842,12 +25842,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -25881,10 +25881,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="O132" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
@@ -25993,12 +25993,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -26032,10 +26032,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="O133" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -26190,7 +26190,7 @@
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
@@ -26227,12 +26227,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -26266,10 +26266,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
@@ -26378,12 +26378,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -26417,10 +26417,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="O135" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
@@ -26612,12 +26612,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -26651,10 +26651,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
@@ -26763,12 +26763,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -26802,10 +26802,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="O137" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
@@ -26997,12 +26997,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -27036,10 +27036,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O138" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
@@ -27148,12 +27148,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -27187,10 +27187,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O139" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -27345,7 +27345,7 @@
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
@@ -27382,12 +27382,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -27421,10 +27421,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="O140" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
@@ -27533,12 +27533,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -27572,10 +27572,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="O141" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
@@ -27767,12 +27767,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -27806,10 +27806,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
@@ -27918,12 +27918,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -27957,10 +27957,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -28115,7 +28115,7 @@
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
@@ -28152,12 +28152,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -28191,22 +28191,14 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -28221,7 +28213,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
@@ -28231,55 +28223,55 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -28311,12 +28303,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -28350,29 +28342,29 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Nephropathia epidemica</t>
+          <t>流行性出血热</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -28382,7 +28374,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -28397,7 +28389,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -28432,17 +28424,17 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -28455,7 +28447,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
@@ -28465,55 +28457,55 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -28545,12 +28537,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -28584,13 +28576,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>0.09344880428283346</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -28599,7 +28591,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_NO_FHI_402_MONTHLY</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -28624,7 +28616,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_NO_FHI_402_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -28637,42 +28629,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28704,12 +28696,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -28743,29 +28735,29 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_NO_FHI_402_MONTHLY</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_NO_FHI_402_MONTHLY</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>Sorkfeber</t>
+          <t>Nephropathia epidemica</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -28790,7 +28782,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -28825,17 +28817,17 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Swedish source category is nephropathia epidemica.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -28858,7 +28850,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_NO_FHI_402_MONTHLY</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -28871,42 +28863,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28938,12 +28930,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -28968,22 +28960,22 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R148" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.09344880428283346</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -28992,7 +28984,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -29017,7 +29009,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -29030,42 +29022,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29097,12 +29089,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -29127,38 +29119,38 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O149" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Nephropathia epidemica</t>
+          <t>Sorkfeber</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -29183,7 +29175,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -29218,17 +29210,17 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Swedish source category is nephropathia epidemica.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29251,7 +29243,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -29264,42 +29256,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29331,12 +29323,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -29370,22 +29362,14 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>14</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0.1308283259959668</v>
+        <v>0</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -29400,7 +29384,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
@@ -29410,55 +29394,55 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -29490,12 +29474,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -29529,29 +29513,29 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Sorkfeber</t>
+          <t>流行性出血热</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -29561,7 +29545,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -29576,7 +29560,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -29611,17 +29595,17 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Swedish source category is nephropathia epidemica.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -29634,7 +29618,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -29644,55 +29628,55 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -29724,12 +29708,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -29754,31 +29738,23 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -29793,7 +29769,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -29803,55 +29779,55 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -29883,12 +29859,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -29913,38 +29889,38 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_402_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Nephropathia epidemica</t>
+          <t>流行性出血热</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -29954,7 +29930,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -29969,7 +29945,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -30004,17 +29980,17 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30027,63 +30003,3167 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>7</v>
+      </c>
+      <c r="O154" t="n">
+        <v>7</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>7</v>
+      </c>
+      <c r="O155" t="n">
+        <v>7</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>4</v>
+      </c>
+      <c r="O156" t="n">
+        <v>4</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>4</v>
+      </c>
+      <c r="O157" t="n">
+        <v>4</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>6</v>
+      </c>
+      <c r="O158" t="n">
+        <v>6</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>6</v>
+      </c>
+      <c r="O159" t="n">
+        <v>6</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>5</v>
+      </c>
+      <c r="O160" t="n">
+        <v>5</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>5</v>
+      </c>
+      <c r="O161" t="n">
+        <v>5</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_HFRS; SER_CN_PROV_REPORT_HFRS</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>1</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ153" t="inlineStr">
+      <c r="AQ164" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS153" t="inlineStr">
+      <c r="AS164" t="inlineStr">
         <is>
           <t>SER_NO_FHI_402_MONTHLY</t>
         </is>
       </c>
-      <c r="AT153" t="n">
+      <c r="AT164" t="n">
         <v>1</v>
       </c>
-      <c r="AU153" t="inlineStr">
+      <c r="AU164" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV153" t="inlineStr">
+      <c r="AV164" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW153" t="inlineStr">
+      <c r="AW164" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX153" t="inlineStr">
+      <c r="AX164" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY153" t="inlineStr">
+      <c r="AY164" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ153" t="inlineStr">
+      <c r="AZ164" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA153" t="inlineStr">
+      <c r="BA164" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB153" t="inlineStr">
+      <c r="BB164" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC153" t="inlineStr">
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Nephropathia epidemica</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>14</v>
+      </c>
+      <c r="O166" t="n">
+        <v>14</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.1308283259959668</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>14</v>
+      </c>
+      <c r="O167" t="n">
+        <v>14</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Sorkfeber</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Swedish source category is nephropathia epidemica.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Nephropathia epidemica</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -30205,7 +33285,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -30215,7 +33295,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -30235,7 +33315,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -30267,7 +33347,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>785</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d163/2026-2029.xlsx
+++ b/diseases/d163/2026-2029.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -24576,7 +24576,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -32308,7 +32308,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -32843,13 +32843,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -33002,10 +33002,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33347,7 +33347,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d163/2026-2029.xlsx
+++ b/diseases/d163/2026-2029.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -24576,7 +24576,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -32308,7 +32308,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33094,7 +33094,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33164,6 +33164,792 @@
         </is>
       </c>
       <c r="BC169" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>22</v>
+      </c>
+      <c r="O170" t="n">
+        <v>22</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.2055873694222336</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>22</v>
+      </c>
+      <c r="O171" t="n">
+        <v>22</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Sorkfeber</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Swedish source category is nephropathia epidemica.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_NEPHROPATHIA</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>hantavirus-hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D163</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Hantavirus hemorrhagic fever</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>汉他病毒出血热</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Nephropathia epidemica</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS renal hantavirus syndrome category.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_402_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -33202,7 +33988,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -33285,7 +34071,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -33295,7 +34081,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -33315,7 +34101,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -33347,7 +34133,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>834</v>
+        <v>856</v>
       </c>
     </row>
     <row r="16">
